--- a/input/assets/Mappings/M11 to FHIR Mapping 02.xlsx
+++ b/input/assets/Mappings/M11 to FHIR Mapping 02.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Filing\UDP\IG_HL7\input\assets\Mappings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A76555-0443-4D8D-9B79-B3BB6774846B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA03CCFC-F82C-446F-B21D-1DB53D0EDAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9120" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9120" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="1" r:id="rId1"/>
-    <sheet name="Mapping" sheetId="2" r:id="rId2"/>
-    <sheet name="Mapping Macros" sheetId="3" r:id="rId3"/>
-    <sheet name="Narrative Section Mapping" sheetId="4" r:id="rId4"/>
+    <sheet name="Licenses" sheetId="5" r:id="rId2"/>
+    <sheet name="Mapping" sheetId="2" r:id="rId3"/>
+    <sheet name="Mapping Macros" sheetId="3" r:id="rId4"/>
+    <sheet name="Narrative Section Mapping" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Mapping!$A$2:$V$327</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Mapping!$A$2:$V$327</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5747" uniqueCount="1926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5756" uniqueCount="1935">
   <si>
     <t>USDM Version</t>
   </si>
@@ -11432,12 +11433,85 @@
   <si>
     <t>FHIR Mapping</t>
   </si>
+  <si>
+    <t>Licenses</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">This mapping spreadsheet uses content from ICH and CDISC.  This is done under terms of the licenses which are detailed in the Implementation Guide under </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Licenses </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>and are reproduced here:</t>
+    </r>
+  </si>
+  <si>
+    <t>ICH</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HL7 Vulcan acknowledges that ICH is the copyright holder for the ICH M11 Harmonised Guideline CeSHarP. 
+Use of ICH M11 Section Headings and Fields within the mapping spreadsheet, the creation of FHIR Profiles representing the M11 structures and the representation of M11 terminology structures within FHIR value sets is under the terms of the custom license provided in the ICH M11documents.  That text is reproduced here:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Legal notice: This document is protected by copyright and may, with the exception of the ICH logo,  be used, reproduced, incorporated into other works, adapted, modified, translated or distributed  under a public license provided that ICH's copyright in the document is acknowledged at all times.  In case of any adaption, modification or translation of the document, reasonable steps must be  taken to clearly label, demarcate or otherwise identify that changes were made to or based on the  original document. Any impression that the adaption, modification or translation of the original  document is endorsed or sponsored by the ICH must be avoided.   The document is provided "as is" without warranty of any kind. In no event shall the ICH or the  authors of the original document be liable for any claim, damages or other liability arising from  the use of the document.   The above-mentioned permissions do not apply to content supplied by third parties. Therefore, for  documents where the copyright vests in a third party, permission for reproduction must be obtained  from this copyright holder.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>CDISC</t>
+  </si>
+  <si>
+    <t>Content based on [DDF-RA (GitHub)]</t>
+  </si>
+  <si>
+    <t>https://github.com/cdisc-org/DDF-RA</t>
+  </si>
+  <si>
+    <t>used under the CC-BY-4.0 license.</t>
+  </si>
+  <si>
+    <t>https://creativecommons.org/licenses/by/4.0/</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11595,6 +11669,13 @@
       <b/>
       <sz val="11"/>
       <color theme="7" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -11790,7 +11871,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -11909,6 +11990,15 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -11916,21 +12006,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11941,6 +12016,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -12503,7 +12593,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="78.75" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A34" s="16" t="s">
         <v>36</v>
       </c>
@@ -12525,6 +12615,69 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89119ED6-9659-4260-936E-D9E5A86C5C5F}">
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="65.86328125" style="53" customWidth="1"/>
+    <col min="2" max="16384" width="9.06640625" style="53"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+      <c r="A1" s="52" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A3" s="53" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" s="54" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="313.5" x14ac:dyDescent="0.45">
+      <c r="A6" s="53" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" s="54" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" s="53" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" s="55" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" s="53" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" s="55" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A10" r:id="rId1" xr:uid="{758900B7-DCF0-42BB-BD8D-2F3D542CA5D8}"/>
+    <hyperlink ref="A12" r:id="rId2" xr:uid="{C463D704-08BD-42CB-8383-998261C73138}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V327"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -12552,34 +12705,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.45">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="45" t="s">
         <v>1078</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="43" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="46" t="s">
         <v>1079</v>
       </c>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="50" t="s">
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="48" t="s">
         <v>1925</v>
       </c>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="52"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="50"/>
     </row>
     <row r="2" spans="1:22" ht="21" x14ac:dyDescent="0.45">
       <c r="A2" s="29" t="s">
@@ -12869,7 +13022,7 @@
       <c r="S6" s="20" t="s">
         <v>1753</v>
       </c>
-      <c r="T6" s="46" t="s">
+      <c r="T6" s="20" t="s">
         <v>1754</v>
       </c>
       <c r="U6" s="20"/>
@@ -14477,7 +14630,7 @@
       <c r="Q34" s="5" t="s">
         <v>1090</v>
       </c>
-      <c r="R34" s="47" t="s">
+      <c r="R34" s="42" t="s">
         <v>1296</v>
       </c>
       <c r="S34" s="20" t="s">
@@ -14486,7 +14639,7 @@
       <c r="T34" s="20" t="s">
         <v>1770</v>
       </c>
-      <c r="U34" s="48" t="s">
+      <c r="U34" s="43" t="s">
         <v>1297</v>
       </c>
       <c r="V34" s="20"/>
@@ -15247,7 +15400,7 @@
       <c r="U47" s="20" t="s">
         <v>1295</v>
       </c>
-      <c r="V47" s="49" t="s">
+      <c r="V47" s="44" t="s">
         <v>1894</v>
       </c>
     </row>
@@ -30369,7 +30522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ECE0B3C-CA23-45B2-8FEB-CC3160A92D68}">
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -30600,7 +30753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F42060E6-22CD-490B-917F-4AFD48DC2F7D}">
   <dimension ref="A1:G163"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -30625,17 +30778,17 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="23" customFormat="1" ht="21" x14ac:dyDescent="0.45">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="45" t="s">
         <v>1078</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="45" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="51" t="s">
         <v>1361</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
     </row>
     <row r="5" spans="1:7" s="23" customFormat="1" ht="21" x14ac:dyDescent="0.45">
       <c r="A5" s="29" t="s">
@@ -30960,7 +31113,7 @@
       </c>
       <c r="G18" s="20"/>
     </row>
-    <row r="19" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A19" s="14" t="s">
         <v>1393</v>
       </c>
@@ -31006,7 +31159,7 @@
       </c>
       <c r="G20" s="20"/>
     </row>
-    <row r="21" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A21" s="14" t="s">
         <v>1397</v>
       </c>
@@ -31210,7 +31363,7 @@
       </c>
       <c r="G29" s="20"/>
     </row>
-    <row r="30" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A30" s="14" t="s">
         <v>1415</v>
       </c>
@@ -31276,7 +31429,7 @@
       </c>
       <c r="G32" s="20"/>
     </row>
-    <row r="33" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A33" s="14" t="s">
         <v>1421</v>
       </c>
@@ -31320,7 +31473,7 @@
       </c>
       <c r="G34" s="20"/>
     </row>
-    <row r="35" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A35" s="14" t="s">
         <v>1425</v>
       </c>
@@ -31390,7 +31543,7 @@
       </c>
       <c r="G37" s="20"/>
     </row>
-    <row r="38" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A38" s="14" t="s">
         <v>1431</v>
       </c>
@@ -31436,7 +31589,7 @@
       </c>
       <c r="G39" s="20"/>
     </row>
-    <row r="40" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A40" s="14" t="s">
         <v>1435</v>
       </c>
@@ -31532,7 +31685,7 @@
       </c>
       <c r="G43" s="20"/>
     </row>
-    <row r="44" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A44" s="14" t="s">
         <v>1443</v>
       </c>
@@ -31622,7 +31775,7 @@
       </c>
       <c r="G47" s="20"/>
     </row>
-    <row r="48" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A48" s="14" t="s">
         <v>1451</v>
       </c>
@@ -31712,7 +31865,7 @@
       </c>
       <c r="G51" s="20"/>
     </row>
-    <row r="52" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A52" s="14" t="s">
         <v>1459</v>
       </c>
@@ -31736,7 +31889,7 @@
       </c>
       <c r="G52" s="20"/>
     </row>
-    <row r="53" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A53" s="14" t="s">
         <v>1461</v>
       </c>
@@ -31758,7 +31911,7 @@
       </c>
       <c r="G53" s="20"/>
     </row>
-    <row r="54" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A54" s="14" t="s">
         <v>1463</v>
       </c>
@@ -31780,7 +31933,7 @@
       </c>
       <c r="G54" s="20"/>
     </row>
-    <row r="55" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A55" s="14" t="s">
         <v>1465</v>
       </c>
@@ -31802,7 +31955,7 @@
       </c>
       <c r="G55" s="20"/>
     </row>
-    <row r="56" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A56" s="14" t="s">
         <v>1467</v>
       </c>
@@ -31824,7 +31977,7 @@
       </c>
       <c r="G56" s="20"/>
     </row>
-    <row r="57" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A57" s="14" t="s">
         <v>1469</v>
       </c>
@@ -31846,7 +31999,7 @@
       </c>
       <c r="G57" s="20"/>
     </row>
-    <row r="58" spans="1:7" ht="47.25" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:7" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A58" s="14" t="s">
         <v>1471</v>
       </c>
@@ -31868,7 +32021,7 @@
       </c>
       <c r="G58" s="20"/>
     </row>
-    <row r="59" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A59" s="14" t="s">
         <v>1473</v>
       </c>
@@ -31890,7 +32043,7 @@
       </c>
       <c r="G59" s="20"/>
     </row>
-    <row r="60" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A60" s="14" t="s">
         <v>1475</v>
       </c>
@@ -31912,7 +32065,7 @@
       </c>
       <c r="G60" s="20"/>
     </row>
-    <row r="61" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A61" s="14" t="s">
         <v>1477</v>
       </c>
@@ -31934,7 +32087,7 @@
       </c>
       <c r="G61" s="20"/>
     </row>
-    <row r="62" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:7" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A62" s="14" t="s">
         <v>1479</v>
       </c>
@@ -31956,7 +32109,7 @@
       </c>
       <c r="G62" s="20"/>
     </row>
-    <row r="63" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A63" s="14" t="s">
         <v>1481</v>
       </c>
@@ -32022,7 +32175,7 @@
       </c>
       <c r="G65" s="20"/>
     </row>
-    <row r="66" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A66" s="14" t="s">
         <v>1487</v>
       </c>
@@ -32044,7 +32197,7 @@
       </c>
       <c r="G66" s="20"/>
     </row>
-    <row r="67" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A67" s="14" t="s">
         <v>1489</v>
       </c>
@@ -32066,7 +32219,7 @@
       </c>
       <c r="G67" s="20"/>
     </row>
-    <row r="68" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A68" s="14" t="s">
         <v>1491</v>
       </c>
@@ -32132,7 +32285,7 @@
       </c>
       <c r="G70" s="20"/>
     </row>
-    <row r="71" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A71" s="14" t="s">
         <v>1497</v>
       </c>
@@ -32178,7 +32331,7 @@
       </c>
       <c r="G72" s="20"/>
     </row>
-    <row r="73" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A73" s="14" t="s">
         <v>1501</v>
       </c>
@@ -32200,7 +32353,7 @@
       </c>
       <c r="G73" s="20"/>
     </row>
-    <row r="74" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A74" s="14" t="s">
         <v>1503</v>
       </c>
@@ -32222,7 +32375,7 @@
       </c>
       <c r="G74" s="20"/>
     </row>
-    <row r="75" spans="1:7" ht="47.25" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:7" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A75" s="14" t="s">
         <v>1505</v>
       </c>
@@ -32246,7 +32399,7 @@
       </c>
       <c r="G75" s="20"/>
     </row>
-    <row r="76" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:7" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A76" s="14" t="s">
         <v>1507</v>
       </c>
@@ -32268,7 +32421,7 @@
       </c>
       <c r="G76" s="20"/>
     </row>
-    <row r="77" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A77" s="14" t="s">
         <v>1509</v>
       </c>
@@ -32290,7 +32443,7 @@
       </c>
       <c r="G77" s="20"/>
     </row>
-    <row r="78" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A78" s="14" t="s">
         <v>1511</v>
       </c>
@@ -32334,7 +32487,7 @@
       </c>
       <c r="G79" s="20"/>
     </row>
-    <row r="80" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A80" s="14" t="s">
         <v>1515</v>
       </c>
@@ -32378,7 +32531,7 @@
       </c>
       <c r="G81" s="20"/>
     </row>
-    <row r="82" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A82" s="14" t="s">
         <v>1519</v>
       </c>
@@ -32402,7 +32555,7 @@
       </c>
       <c r="G82" s="20"/>
     </row>
-    <row r="83" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A83" s="14" t="s">
         <v>1521</v>
       </c>
@@ -32424,7 +32577,7 @@
       </c>
       <c r="G83" s="20"/>
     </row>
-    <row r="84" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A84" s="14" t="s">
         <v>1523</v>
       </c>
@@ -32446,7 +32599,7 @@
       </c>
       <c r="G84" s="20"/>
     </row>
-    <row r="85" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A85" s="14" t="s">
         <v>1525</v>
       </c>
@@ -32468,7 +32621,7 @@
       </c>
       <c r="G85" s="20"/>
     </row>
-    <row r="86" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A86" s="14" t="s">
         <v>1527</v>
       </c>
@@ -32600,7 +32753,7 @@
       </c>
       <c r="G91" s="20"/>
     </row>
-    <row r="92" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A92" s="14" t="s">
         <v>1539</v>
       </c>
@@ -32666,7 +32819,7 @@
       </c>
       <c r="G94" s="20"/>
     </row>
-    <row r="95" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A95" s="14" t="s">
         <v>1545</v>
       </c>
@@ -32754,7 +32907,7 @@
       </c>
       <c r="G98" s="20"/>
     </row>
-    <row r="99" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A99" s="14" t="s">
         <v>1553</v>
       </c>
@@ -32776,7 +32929,7 @@
       </c>
       <c r="G99" s="20"/>
     </row>
-    <row r="100" spans="1:7" ht="63" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:7" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A100" s="14" t="s">
         <v>1555</v>
       </c>
@@ -32844,7 +32997,7 @@
       </c>
       <c r="G102" s="20"/>
     </row>
-    <row r="103" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A103" s="14" t="s">
         <v>1561</v>
       </c>
@@ -32866,7 +33019,7 @@
       </c>
       <c r="G103" s="20"/>
     </row>
-    <row r="104" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A104" s="14" t="s">
         <v>1563</v>
       </c>
@@ -32888,7 +33041,7 @@
       </c>
       <c r="G104" s="20"/>
     </row>
-    <row r="105" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A105" s="14" t="s">
         <v>1565</v>
       </c>
@@ -32910,7 +33063,7 @@
       </c>
       <c r="G105" s="20"/>
     </row>
-    <row r="106" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A106" s="14" t="s">
         <v>1567</v>
       </c>
@@ -32998,7 +33151,7 @@
       </c>
       <c r="G109" s="20"/>
     </row>
-    <row r="110" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A110" s="14" t="s">
         <v>1575</v>
       </c>
@@ -33020,7 +33173,7 @@
       </c>
       <c r="G110" s="20"/>
     </row>
-    <row r="111" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A111" s="14" t="s">
         <v>1577</v>
       </c>
@@ -33042,7 +33195,7 @@
       </c>
       <c r="G111" s="20"/>
     </row>
-    <row r="112" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:7" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A112" s="14" t="s">
         <v>1579</v>
       </c>
@@ -33064,7 +33217,7 @@
       </c>
       <c r="G112" s="20"/>
     </row>
-    <row r="113" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A113" s="14" t="s">
         <v>1581</v>
       </c>
@@ -33086,7 +33239,7 @@
       </c>
       <c r="G113" s="20"/>
     </row>
-    <row r="114" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A114" s="14" t="s">
         <v>1583</v>
       </c>
@@ -33108,7 +33261,7 @@
       </c>
       <c r="G114" s="20"/>
     </row>
-    <row r="115" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A115" s="14" t="s">
         <v>1585</v>
       </c>
@@ -33220,7 +33373,7 @@
       </c>
       <c r="G119" s="20"/>
     </row>
-    <row r="120" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A120" s="14" t="s">
         <v>1595</v>
       </c>
@@ -33242,7 +33395,7 @@
       </c>
       <c r="G120" s="20"/>
     </row>
-    <row r="121" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A121" s="14" t="s">
         <v>1597</v>
       </c>
@@ -33308,7 +33461,7 @@
       </c>
       <c r="G123" s="20"/>
     </row>
-    <row r="124" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A124" s="14" t="s">
         <v>1603</v>
       </c>
@@ -33330,7 +33483,7 @@
       </c>
       <c r="G124" s="20"/>
     </row>
-    <row r="125" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A125" s="14" t="s">
         <v>1605</v>
       </c>
@@ -33396,7 +33549,7 @@
       </c>
       <c r="G127" s="20"/>
     </row>
-    <row r="128" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A128" s="14" t="s">
         <v>1611</v>
       </c>
@@ -33462,7 +33615,7 @@
       </c>
       <c r="G130" s="20"/>
     </row>
-    <row r="131" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A131" s="14" t="s">
         <v>1617</v>
       </c>
@@ -33484,7 +33637,7 @@
       </c>
       <c r="G131" s="20"/>
     </row>
-    <row r="132" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A132" s="14" t="s">
         <v>1619</v>
       </c>
@@ -33550,7 +33703,7 @@
       </c>
       <c r="G134" s="20"/>
     </row>
-    <row r="135" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A135" s="14" t="s">
         <v>1625</v>
       </c>
@@ -33684,7 +33837,7 @@
       </c>
       <c r="G140" s="20"/>
     </row>
-    <row r="141" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A141" s="14" t="s">
         <v>1637</v>
       </c>
@@ -33708,7 +33861,7 @@
       </c>
       <c r="G141" s="20"/>
     </row>
-    <row r="142" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A142" s="14" t="s">
         <v>1639</v>
       </c>
@@ -33818,7 +33971,7 @@
       </c>
       <c r="G146" s="20"/>
     </row>
-    <row r="147" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A147" s="14" t="s">
         <v>1649</v>
       </c>
@@ -33840,7 +33993,7 @@
       </c>
       <c r="G147" s="20"/>
     </row>
-    <row r="148" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:7" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A148" s="14" t="s">
         <v>1651</v>
       </c>
@@ -34106,7 +34259,7 @@
       </c>
       <c r="G159" s="20"/>
     </row>
-    <row r="160" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A160" s="14" t="s">
         <v>1675</v>
       </c>
@@ -34150,7 +34303,7 @@
       </c>
       <c r="G161" s="20"/>
     </row>
-    <row r="162" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A162" s="14" t="s">
         <v>1679</v>
       </c>
@@ -34208,12 +34361,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5b833577-d5f3-4c92-a991-e0f5e5f065ff">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f82658c3-1dde-4375-8027-c01e071e8904" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -34444,20 +34599,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5b833577-d5f3-4c92-a991-e0f5e5f065ff">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f82658c3-1dde-4375-8027-c01e071e8904" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D138339-0D57-487F-9E81-FE386A716C4B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52BB9F-889F-474C-B55A-D27BEDC8B0F9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5b833577-d5f3-4c92-a991-e0f5e5f065ff"/>
+    <ds:schemaRef ds:uri="f82658c3-1dde-4375-8027-c01e071e8904"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34482,12 +34638,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52BB9F-889F-474C-B55A-D27BEDC8B0F9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D138339-0D57-487F-9E81-FE386A716C4B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5b833577-d5f3-4c92-a991-e0f5e5f065ff"/>
-    <ds:schemaRef ds:uri="f82658c3-1dde-4375-8027-c01e071e8904"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>